--- a/unilabos/devices/workstation/XUSE/templates/马弗炉参数模板.xlsx
+++ b/unilabos/devices/workstation/XUSE/templates/马弗炉参数模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="14055" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8080"/>
   </bookViews>
   <sheets>
     <sheet name="马弗炉1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="48">
   <si>
     <t>参数名</t>
   </si>
@@ -167,15 +167,6 @@
   </si>
   <si>
     <t>上限报警温度</t>
-  </si>
-  <si>
-    <t>温度参数1</t>
-  </si>
-  <si>
-    <t>温度参数2</t>
-  </si>
-  <si>
-    <t>温度参数3</t>
   </si>
   <si>
     <t>输出功率上限</t>
@@ -653,148 +644,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1153,10 +1144,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B50"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <dimension ref="A1:B47"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="15.125" customWidth="1"/>
+    <col min="1" max="1" width="15.1272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1167,396 +1158,234 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+    </row>
+    <row r="3" spans="1:1">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+    </row>
+    <row r="4" spans="1:1">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+    </row>
+    <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+    </row>
+    <row r="6" spans="1:1">
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+    </row>
+    <row r="7" spans="1:1">
       <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+    </row>
+    <row r="8" spans="1:1">
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+    </row>
+    <row r="9" spans="1:1">
       <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="B9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+    </row>
+    <row r="10" spans="1:1">
       <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="B10">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+    </row>
+    <row r="11" spans="1:1">
       <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+    </row>
+    <row r="12" spans="1:1">
       <c r="A12" t="s">
         <v>12</v>
       </c>
-      <c r="B12">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+    </row>
+    <row r="13" spans="1:1">
       <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="B13">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+    </row>
+    <row r="14" spans="1:1">
       <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B14">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+    </row>
+    <row r="15" spans="1:1">
       <c r="A15" t="s">
         <v>15</v>
       </c>
-      <c r="B15">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+    </row>
+    <row r="16" spans="1:1">
       <c r="A16" t="s">
         <v>16</v>
       </c>
-      <c r="B16">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+    </row>
+    <row r="17" spans="1:1">
       <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="B17">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
+    </row>
+    <row r="18" spans="1:1">
       <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="B18">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+    </row>
+    <row r="19" spans="1:1">
       <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="B19">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
+    </row>
+    <row r="20" spans="1:1">
       <c r="A20" t="s">
         <v>20</v>
       </c>
-      <c r="B20">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
+    </row>
+    <row r="21" spans="1:1">
       <c r="A21" t="s">
         <v>21</v>
       </c>
-      <c r="B21">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
+    </row>
+    <row r="22" spans="1:1">
       <c r="A22" t="s">
         <v>22</v>
       </c>
-      <c r="B22">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
+    </row>
+    <row r="23" spans="1:1">
       <c r="A23" t="s">
         <v>23</v>
       </c>
-      <c r="B23">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
+    </row>
+    <row r="24" spans="1:1">
       <c r="A24" t="s">
         <v>24</v>
       </c>
-      <c r="B24">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
+    </row>
+    <row r="25" spans="1:1">
       <c r="A25" t="s">
         <v>25</v>
       </c>
-      <c r="B25">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
+    </row>
+    <row r="26" spans="1:1">
       <c r="A26" t="s">
         <v>26</v>
       </c>
-      <c r="B26">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
+    </row>
+    <row r="27" spans="1:1">
       <c r="A27" t="s">
         <v>27</v>
       </c>
-      <c r="B27">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
+    </row>
+    <row r="28" spans="1:1">
       <c r="A28" t="s">
         <v>28</v>
       </c>
-      <c r="B28">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
+    </row>
+    <row r="29" spans="1:1">
       <c r="A29" t="s">
         <v>29</v>
       </c>
-      <c r="B29">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
+    </row>
+    <row r="30" spans="1:1">
       <c r="A30" t="s">
         <v>30</v>
       </c>
-      <c r="B30">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
+    </row>
+    <row r="31" spans="1:1">
       <c r="A31" t="s">
         <v>31</v>
       </c>
-      <c r="B31">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
+    </row>
+    <row r="32" spans="1:1">
       <c r="A32" t="s">
         <v>32</v>
       </c>
-      <c r="B32">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
+    </row>
+    <row r="33" spans="1:1">
       <c r="A33" t="s">
         <v>33</v>
       </c>
-      <c r="B33">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
+    </row>
+    <row r="34" spans="1:1">
       <c r="A34" t="s">
         <v>34</v>
       </c>
-      <c r="B34">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
+    </row>
+    <row r="35" spans="1:1">
       <c r="A35" t="s">
         <v>35</v>
       </c>
-      <c r="B35">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
+    </row>
+    <row r="36" spans="1:1">
       <c r="A36" t="s">
         <v>36</v>
       </c>
-      <c r="B36">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
+    </row>
+    <row r="37" spans="1:1">
       <c r="A37" t="s">
         <v>37</v>
       </c>
-      <c r="B37">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
+    </row>
+    <row r="38" spans="1:1">
       <c r="A38" t="s">
         <v>38</v>
       </c>
-      <c r="B38">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
+    </row>
+    <row r="39" spans="1:1">
       <c r="A39" t="s">
         <v>39</v>
       </c>
-      <c r="B39">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
+    </row>
+    <row r="40" spans="1:1">
       <c r="A40" t="s">
         <v>40</v>
       </c>
-      <c r="B40">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
+    </row>
+    <row r="41" spans="1:1">
       <c r="A41" t="s">
         <v>41</v>
       </c>
-      <c r="B41">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
+    </row>
+    <row r="42" spans="1:1">
       <c r="A42" t="s">
         <v>42</v>
       </c>
-      <c r="B42">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
+    </row>
+    <row r="43" spans="1:1">
       <c r="A43" t="s">
         <v>43</v>
       </c>
-      <c r="B43">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
+    </row>
+    <row r="44" spans="1:1">
       <c r="A44" t="s">
         <v>44</v>
       </c>
-      <c r="B44">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
+    </row>
+    <row r="45" spans="1:1">
       <c r="A45" t="s">
         <v>45</v>
       </c>
-      <c r="B45">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
+    </row>
+    <row r="46" spans="1:1">
       <c r="A46" t="s">
         <v>46</v>
       </c>
-      <c r="B46">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
+    </row>
+    <row r="47" spans="1:1">
       <c r="A47" t="s">
         <v>47</v>
-      </c>
-      <c r="B47">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" t="s">
-        <v>48</v>
-      </c>
-      <c r="B48">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" t="s">
-        <v>49</v>
-      </c>
-      <c r="B49">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" t="s">
-        <v>50</v>
-      </c>
-      <c r="B50">
-        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1568,10 +1397,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B50"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <dimension ref="A1:B47"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="15.125" customWidth="1"/>
+    <col min="1" max="1" width="15.1272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1582,396 +1411,234 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+    </row>
+    <row r="3" spans="1:1">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+    </row>
+    <row r="4" spans="1:1">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+    </row>
+    <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+    </row>
+    <row r="6" spans="1:1">
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+    </row>
+    <row r="7" spans="1:1">
       <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B7">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+    </row>
+    <row r="8" spans="1:1">
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+    </row>
+    <row r="9" spans="1:1">
       <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="B9">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+    </row>
+    <row r="10" spans="1:1">
       <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="B10">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+    </row>
+    <row r="11" spans="1:1">
       <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B11">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+    </row>
+    <row r="12" spans="1:1">
       <c r="A12" t="s">
         <v>12</v>
       </c>
-      <c r="B12">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+    </row>
+    <row r="13" spans="1:1">
       <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="B13">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+    </row>
+    <row r="14" spans="1:1">
       <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B14">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+    </row>
+    <row r="15" spans="1:1">
       <c r="A15" t="s">
         <v>15</v>
       </c>
-      <c r="B15">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+    </row>
+    <row r="16" spans="1:1">
       <c r="A16" t="s">
         <v>16</v>
       </c>
-      <c r="B16">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+    </row>
+    <row r="17" spans="1:1">
       <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="B17">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
+    </row>
+    <row r="18" spans="1:1">
       <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="B18">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+    </row>
+    <row r="19" spans="1:1">
       <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="B19">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
+    </row>
+    <row r="20" spans="1:1">
       <c r="A20" t="s">
         <v>20</v>
       </c>
-      <c r="B20">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
+    </row>
+    <row r="21" spans="1:1">
       <c r="A21" t="s">
         <v>21</v>
       </c>
-      <c r="B21">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
+    </row>
+    <row r="22" spans="1:1">
       <c r="A22" t="s">
         <v>22</v>
       </c>
-      <c r="B22">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
+    </row>
+    <row r="23" spans="1:1">
       <c r="A23" t="s">
         <v>23</v>
       </c>
-      <c r="B23">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
+    </row>
+    <row r="24" spans="1:1">
       <c r="A24" t="s">
         <v>24</v>
       </c>
-      <c r="B24">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
+    </row>
+    <row r="25" spans="1:1">
       <c r="A25" t="s">
         <v>25</v>
       </c>
-      <c r="B25">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
+    </row>
+    <row r="26" spans="1:1">
       <c r="A26" t="s">
         <v>26</v>
       </c>
-      <c r="B26">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
+    </row>
+    <row r="27" spans="1:1">
       <c r="A27" t="s">
         <v>27</v>
       </c>
-      <c r="B27">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
+    </row>
+    <row r="28" spans="1:1">
       <c r="A28" t="s">
         <v>28</v>
       </c>
-      <c r="B28">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
+    </row>
+    <row r="29" spans="1:1">
       <c r="A29" t="s">
         <v>29</v>
       </c>
-      <c r="B29">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
+    </row>
+    <row r="30" spans="1:1">
       <c r="A30" t="s">
         <v>30</v>
       </c>
-      <c r="B30">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
+    </row>
+    <row r="31" spans="1:1">
       <c r="A31" t="s">
         <v>31</v>
       </c>
-      <c r="B31">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
+    </row>
+    <row r="32" spans="1:1">
       <c r="A32" t="s">
         <v>32</v>
       </c>
-      <c r="B32">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
+    </row>
+    <row r="33" spans="1:1">
       <c r="A33" t="s">
         <v>33</v>
       </c>
-      <c r="B33">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
+    </row>
+    <row r="34" spans="1:1">
       <c r="A34" t="s">
         <v>34</v>
       </c>
-      <c r="B34">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
+    </row>
+    <row r="35" spans="1:1">
       <c r="A35" t="s">
         <v>35</v>
       </c>
-      <c r="B35">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
+    </row>
+    <row r="36" spans="1:1">
       <c r="A36" t="s">
         <v>36</v>
       </c>
-      <c r="B36">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
+    </row>
+    <row r="37" spans="1:1">
       <c r="A37" t="s">
         <v>37</v>
       </c>
-      <c r="B37">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
+    </row>
+    <row r="38" spans="1:1">
       <c r="A38" t="s">
         <v>38</v>
       </c>
-      <c r="B38">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
+    </row>
+    <row r="39" spans="1:1">
       <c r="A39" t="s">
         <v>39</v>
       </c>
-      <c r="B39">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
+    </row>
+    <row r="40" spans="1:1">
       <c r="A40" t="s">
         <v>40</v>
       </c>
-      <c r="B40">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
+    </row>
+    <row r="41" spans="1:1">
       <c r="A41" t="s">
         <v>41</v>
       </c>
-      <c r="B41">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
+    </row>
+    <row r="42" spans="1:1">
       <c r="A42" t="s">
         <v>42</v>
       </c>
-      <c r="B42">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
+    </row>
+    <row r="43" spans="1:1">
       <c r="A43" t="s">
         <v>43</v>
       </c>
-      <c r="B43">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
+    </row>
+    <row r="44" spans="1:1">
       <c r="A44" t="s">
         <v>44</v>
       </c>
-      <c r="B44">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
+    </row>
+    <row r="45" spans="1:1">
       <c r="A45" t="s">
         <v>45</v>
       </c>
-      <c r="B45">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
+    </row>
+    <row r="46" spans="1:1">
       <c r="A46" t="s">
         <v>46</v>
       </c>
-      <c r="B46">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
+    </row>
+    <row r="47" spans="1:1">
       <c r="A47" t="s">
         <v>47</v>
-      </c>
-      <c r="B47">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" t="s">
-        <v>48</v>
-      </c>
-      <c r="B48">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" t="s">
-        <v>49</v>
-      </c>
-      <c r="B49">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" t="s">
-        <v>50</v>
-      </c>
-      <c r="B50">
-        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -1983,8 +1650,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B50"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <dimension ref="A1:B47"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -2222,21 +1889,6 @@
     <row r="47" spans="1:1">
       <c r="A47" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -2248,8 +1900,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B50"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <dimension ref="A1:B47"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -2487,21 +2139,6 @@
     <row r="47" spans="1:1">
       <c r="A47" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -2513,8 +2150,8 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B50"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <dimension ref="A1:B47"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -2752,21 +2389,6 @@
     <row r="47" spans="1:1">
       <c r="A47" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -2778,8 +2400,8 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B50"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <dimension ref="A1:B47"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -3017,21 +2639,6 @@
     <row r="47" spans="1:1">
       <c r="A47" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
